--- a/Week 4/PivotTable_tutorial.xlsx
+++ b/Week 4/PivotTable_tutorial.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A35553C-407A-47E4-9492-9A074E23D588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{2A35553C-407A-47E4-9492-9A074E23D588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02CDFF7C-E2A4-4319-9963-6F21C61BBCBF}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" tabRatio="910" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId23"/>
-    <pivotCache cacheId="1" r:id="rId24"/>
+    <pivotCache cacheId="11" r:id="rId24"/>
     <pivotCache cacheId="2" r:id="rId25"/>
     <pivotCache cacheId="3" r:id="rId26"/>
     <pivotCache cacheId="4" r:id="rId27"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="95">
   <si>
     <t>Go back to top by pressing CTRL+HOME. To start the tour, press CTRL+PAGE DOWN.</t>
   </si>
@@ -392,7 +392,7 @@
     <numFmt numFmtId="164" formatCode="dd\-mmm"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,6 +554,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -598,7 +604,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -630,117 +636,6 @@
       <top/>
       <bottom style="thick">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
       </bottom>
       <diagonal/>
     </border>
@@ -801,11 +696,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" applyNumberFormat="0" applyFont="0" applyFill="0" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="15" applyNumberFormat="0" applyFont="0" applyFill="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyFill="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyFill="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5"/>
@@ -852,31 +747,22 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="11" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="12"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="13" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" xfId="14" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="14" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="12"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="13" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="14" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="5" fontId="2" fillId="7" borderId="15" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="15" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="2" fillId="7" borderId="6" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="6" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -885,6 +771,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="15">
     <cellStyle name="20% - Accent6" xfId="12" builtinId="50" customBuiltin="1"/>
@@ -5963,8 +5850,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5675948" y="1172845"/>
-          <a:ext cx="919797" cy="670923"/>
+          <a:off x="5754688" y="1171575"/>
+          <a:ext cx="928687" cy="672193"/>
           <a:chOff x="5756275" y="1171575"/>
           <a:chExt cx="930275" cy="672193"/>
         </a:xfrm>
@@ -6107,8 +5994,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2193290" y="1172845"/>
-          <a:ext cx="2967721" cy="940485"/>
+          <a:off x="2209800" y="1171575"/>
+          <a:ext cx="3015981" cy="944295"/>
           <a:chOff x="2209800" y="1171575"/>
           <a:chExt cx="3022331" cy="944295"/>
         </a:xfrm>
@@ -7055,8 +6942,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5629593" y="980440"/>
-          <a:ext cx="966152" cy="672193"/>
+          <a:off x="5707063" y="977900"/>
+          <a:ext cx="976312" cy="672193"/>
           <a:chOff x="5708650" y="977900"/>
           <a:chExt cx="942975" cy="672193"/>
         </a:xfrm>
@@ -7199,8 +7086,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2141855" y="980440"/>
-          <a:ext cx="2972801" cy="940485"/>
+          <a:off x="2162175" y="977900"/>
+          <a:ext cx="3015981" cy="944295"/>
           <a:chOff x="2162175" y="977900"/>
           <a:chExt cx="3022331" cy="944295"/>
         </a:xfrm>
@@ -7360,7 +7247,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>256794</xdr:colOff>
+      <xdr:colOff>371094</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>33528</xdr:rowOff>
     </xdr:to>
@@ -7687,7 +7574,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>256794</xdr:colOff>
+      <xdr:colOff>371094</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -7852,13 +7739,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>677164</xdr:colOff>
+      <xdr:colOff>639064</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>59326</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>364934</xdr:colOff>
+      <xdr:colOff>390334</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>35925</xdr:rowOff>
     </xdr:to>
@@ -8200,13 +8087,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>309563</xdr:colOff>
+      <xdr:colOff>271463</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
+      <xdr:colOff>222250</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>5443</xdr:rowOff>
     </xdr:to>
@@ -8223,8 +8110,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5896293" y="1202690"/>
-          <a:ext cx="919797" cy="458833"/>
+          <a:off x="5973763" y="1200150"/>
+          <a:ext cx="928687" cy="462643"/>
           <a:chOff x="5975350" y="1200150"/>
           <a:chExt cx="930275" cy="462643"/>
         </a:xfrm>
@@ -8350,7 +8237,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>52388</xdr:colOff>
+      <xdr:colOff>14288</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>5443</xdr:rowOff>
     </xdr:to>
@@ -8367,8 +8254,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4681855" y="1202690"/>
-          <a:ext cx="955993" cy="458833"/>
+          <a:off x="4727575" y="1200150"/>
+          <a:ext cx="989013" cy="462643"/>
           <a:chOff x="4733925" y="1200150"/>
           <a:chExt cx="984250" cy="462643"/>
         </a:xfrm>
@@ -9399,8 +9286,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="647113" y="1152252"/>
-          <a:ext cx="2551970" cy="507366"/>
+          <a:off x="656003" y="1154792"/>
+          <a:ext cx="2571020" cy="504826"/>
           <a:chOff x="656003" y="1154792"/>
           <a:chExt cx="2571020" cy="504826"/>
         </a:xfrm>
@@ -9538,8 +9425,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6117908" y="1143000"/>
-          <a:ext cx="913447" cy="471533"/>
+          <a:off x="6192838" y="1143000"/>
+          <a:ext cx="928687" cy="468993"/>
           <a:chOff x="6194425" y="1143000"/>
           <a:chExt cx="930275" cy="468993"/>
         </a:xfrm>
@@ -9700,8 +9587,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4246246" y="1143000"/>
-          <a:ext cx="1734502" cy="471533"/>
+          <a:off x="4289426" y="1143000"/>
+          <a:ext cx="1770062" cy="468993"/>
           <a:chOff x="4295776" y="1143000"/>
           <a:chExt cx="1765299" cy="468993"/>
         </a:xfrm>
@@ -10796,8 +10683,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2879812" y="1633855"/>
-          <a:ext cx="2533294" cy="1350620"/>
+          <a:off x="2931882" y="1635125"/>
+          <a:ext cx="2591714" cy="1349350"/>
           <a:chOff x="2792182" y="1685925"/>
           <a:chExt cx="2467889" cy="1400150"/>
         </a:xfrm>
@@ -11000,7 +10887,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="266700" y="1625601"/>
-          <a:ext cx="1869441" cy="1038274"/>
+          <a:ext cx="1905001" cy="1039544"/>
           <a:chOff x="266700" y="1625601"/>
           <a:chExt cx="1885951" cy="1039544"/>
         </a:xfrm>
@@ -12031,8 +11918,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1068379" y="1809749"/>
-          <a:ext cx="3108651" cy="2239645"/>
+          <a:off x="1082349" y="1809749"/>
+          <a:ext cx="3172151" cy="2238375"/>
           <a:chOff x="1075999" y="1809749"/>
           <a:chExt cx="3153101" cy="2238375"/>
         </a:xfrm>
@@ -13158,8 +13045,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1206500" y="1289050"/>
-          <a:ext cx="2691447" cy="702038"/>
+          <a:off x="1231900" y="1289050"/>
+          <a:ext cx="2732087" cy="700768"/>
           <a:chOff x="1219200" y="1289050"/>
           <a:chExt cx="2720975" cy="700768"/>
         </a:xfrm>
@@ -14948,8 +14835,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2449195" y="1373505"/>
-          <a:ext cx="1524952" cy="624568"/>
+          <a:off x="2486025" y="1374775"/>
+          <a:ext cx="1554162" cy="624568"/>
           <a:chOff x="2466975" y="1374775"/>
           <a:chExt cx="1546224" cy="624568"/>
         </a:xfrm>
@@ -15125,8 +15012,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="848359" y="1365250"/>
-          <a:ext cx="1456689" cy="632823"/>
+          <a:off x="863599" y="1365250"/>
+          <a:ext cx="1479549" cy="634093"/>
           <a:chOff x="857249" y="1365250"/>
           <a:chExt cx="1466849" cy="634093"/>
         </a:xfrm>
@@ -15293,7 +15180,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>199644</xdr:colOff>
+      <xdr:colOff>428244</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>83311</xdr:rowOff>
     </xdr:to>
@@ -15458,13 +15345,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>413131</xdr:colOff>
+      <xdr:colOff>641731</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>135525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>706247</xdr:colOff>
+      <xdr:colOff>934847</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>111141</xdr:rowOff>
     </xdr:to>
@@ -15812,7 +15699,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>199644</xdr:colOff>
+      <xdr:colOff>428244</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
@@ -16009,8 +15896,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="76200" y="595630"/>
-          <a:ext cx="1894841" cy="1381760"/>
+          <a:off x="76200" y="596900"/>
+          <a:ext cx="1911351" cy="1377950"/>
           <a:chOff x="76200" y="596900"/>
           <a:chExt cx="1911351" cy="1377950"/>
         </a:xfrm>
@@ -16411,8 +16298,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2069677" y="595630"/>
-          <a:ext cx="1854201" cy="1734819"/>
+          <a:off x="2091267" y="596900"/>
+          <a:ext cx="1879601" cy="1739899"/>
           <a:chOff x="2091267" y="596900"/>
           <a:chExt cx="1885951" cy="1737815"/>
         </a:xfrm>
@@ -16830,13 +16717,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>358775</xdr:colOff>
+      <xdr:colOff>587375</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
+      <xdr:colOff>514350</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
@@ -16853,8 +16740,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6204585" y="598805"/>
-          <a:ext cx="1906905" cy="1378585"/>
+          <a:off x="6289675" y="600075"/>
+          <a:ext cx="1939925" cy="1374775"/>
           <a:chOff x="6296025" y="600075"/>
           <a:chExt cx="1939925" cy="1374775"/>
         </a:xfrm>
@@ -17278,7 +17165,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
+      <xdr:colOff>495300</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171451</xdr:rowOff>
     </xdr:to>
@@ -17295,8 +17182,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4015740" y="598805"/>
-          <a:ext cx="2099310" cy="864236"/>
+          <a:off x="4057650" y="600075"/>
+          <a:ext cx="2139950" cy="860426"/>
           <a:chOff x="4064000" y="600075"/>
           <a:chExt cx="2139950" cy="860426"/>
         </a:xfrm>
@@ -17810,8 +17697,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>650493</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>4022</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>33528</xdr:rowOff>
     </xdr:to>
@@ -18557,8 +18444,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="688340" y="1007132"/>
-          <a:ext cx="2534285" cy="570208"/>
+          <a:off x="697230" y="1009672"/>
+          <a:ext cx="2550795" cy="565128"/>
           <a:chOff x="697230" y="1009672"/>
           <a:chExt cx="2560320" cy="565128"/>
         </a:xfrm>
@@ -18706,8 +18593,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3941447" y="996971"/>
-          <a:ext cx="2848609" cy="628635"/>
+          <a:off x="3984627" y="996971"/>
+          <a:ext cx="2889249" cy="628635"/>
           <a:chOff x="3986515" y="997256"/>
           <a:chExt cx="2909654" cy="628351"/>
         </a:xfrm>
@@ -19607,8 +19494,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="823595" y="4714875"/>
-          <a:ext cx="6409055" cy="1216025"/>
+          <a:off x="835025" y="4714875"/>
+          <a:ext cx="6537325" cy="1216025"/>
           <a:chOff x="828675" y="4714875"/>
           <a:chExt cx="6511925" cy="1216025"/>
         </a:xfrm>
@@ -20071,8 +19958,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4967605" y="2106930"/>
-          <a:ext cx="1645285" cy="2388870"/>
+          <a:off x="5064125" y="2108200"/>
+          <a:ext cx="1673225" cy="2387600"/>
           <a:chOff x="5038725" y="2108200"/>
           <a:chExt cx="1673225" cy="2387600"/>
         </a:xfrm>
@@ -20938,8 +20825,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="76200" y="598805"/>
-          <a:ext cx="1896746" cy="1378585"/>
+          <a:off x="76200" y="600075"/>
+          <a:ext cx="1914526" cy="1374775"/>
           <a:chOff x="76200" y="600075"/>
           <a:chExt cx="1914526" cy="1374775"/>
         </a:xfrm>
@@ -21300,8 +21187,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2165562" y="598805"/>
-          <a:ext cx="1854201" cy="1901190"/>
+          <a:off x="2183342" y="600075"/>
+          <a:ext cx="1879601" cy="1898650"/>
           <a:chOff x="2183342" y="600075"/>
           <a:chExt cx="1885951" cy="1570445"/>
         </a:xfrm>
@@ -21839,8 +21726,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5893435" y="598805"/>
-          <a:ext cx="1822451" cy="1909444"/>
+          <a:off x="5972175" y="600075"/>
+          <a:ext cx="1847851" cy="1908174"/>
           <a:chOff x="5978525" y="600075"/>
           <a:chExt cx="1847851" cy="1908174"/>
         </a:xfrm>
@@ -22241,8 +22128,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4069079" y="595630"/>
-          <a:ext cx="1786257" cy="1381760"/>
+          <a:off x="4114799" y="596900"/>
+          <a:ext cx="1819277" cy="1377950"/>
           <a:chOff x="4121149" y="596900"/>
           <a:chExt cx="1819277" cy="1377950"/>
         </a:xfrm>
@@ -23468,8 +23355,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2738164" y="2324100"/>
-          <a:ext cx="636116" cy="320501"/>
+          <a:off x="2750864" y="2324100"/>
+          <a:ext cx="633576" cy="319231"/>
           <a:chOff x="10096500" y="4114799"/>
           <a:chExt cx="914400" cy="476251"/>
         </a:xfrm>
@@ -24746,8 +24633,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3881756" y="1007132"/>
-          <a:ext cx="3315795" cy="618475"/>
+          <a:off x="3927476" y="1009672"/>
+          <a:ext cx="3356435" cy="615935"/>
           <a:chOff x="3933826" y="1009672"/>
           <a:chExt cx="3381835" cy="615935"/>
         </a:xfrm>
@@ -25651,8 +25538,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3703954" y="983638"/>
-          <a:ext cx="3589165" cy="641969"/>
+          <a:off x="3743324" y="981098"/>
+          <a:ext cx="3650125" cy="644509"/>
           <a:chOff x="3749674" y="981955"/>
           <a:chExt cx="3661237" cy="643652"/>
         </a:xfrm>
@@ -26590,8 +26477,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="651509" y="1005227"/>
-          <a:ext cx="2544445" cy="620379"/>
+          <a:off x="660399" y="1006497"/>
+          <a:ext cx="2562225" cy="619109"/>
           <a:chOff x="660399" y="1006497"/>
           <a:chExt cx="2562225" cy="619109"/>
         </a:xfrm>
@@ -26739,8 +26626,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3322952" y="1665610"/>
-          <a:ext cx="2553338" cy="1463035"/>
+          <a:off x="3362322" y="1666880"/>
+          <a:ext cx="2574928" cy="1460495"/>
           <a:chOff x="3368672" y="1666880"/>
           <a:chExt cx="2581278" cy="1460495"/>
         </a:xfrm>
@@ -27701,8 +27588,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="661696" y="1126490"/>
-          <a:ext cx="546374" cy="532100"/>
+          <a:off x="665506" y="1123950"/>
+          <a:ext cx="548914" cy="534640"/>
           <a:chOff x="665506" y="1123950"/>
           <a:chExt cx="548914" cy="534640"/>
         </a:xfrm>
@@ -27856,8 +27743,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1234518" y="1127108"/>
-          <a:ext cx="675637" cy="530862"/>
+          <a:off x="1238328" y="1124568"/>
+          <a:ext cx="692147" cy="533402"/>
           <a:chOff x="1238328" y="1124568"/>
           <a:chExt cx="692147" cy="533402"/>
         </a:xfrm>
@@ -28011,8 +27898,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1941551" y="1127108"/>
-          <a:ext cx="624837" cy="530862"/>
+          <a:off x="1960601" y="1124568"/>
+          <a:ext cx="628647" cy="533402"/>
           <a:chOff x="1960601" y="1124568"/>
           <a:chExt cx="628647" cy="533402"/>
         </a:xfrm>
@@ -28166,8 +28053,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2591436" y="1127108"/>
-          <a:ext cx="601342" cy="530862"/>
+          <a:off x="2619376" y="1124568"/>
+          <a:ext cx="600072" cy="533402"/>
           <a:chOff x="2619376" y="1124568"/>
           <a:chExt cx="600072" cy="533402"/>
         </a:xfrm>
@@ -28321,8 +28208,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3996055" y="1297305"/>
-          <a:ext cx="3152140" cy="1831340"/>
+          <a:off x="4041775" y="1298575"/>
+          <a:ext cx="3194050" cy="1828800"/>
           <a:chOff x="4048125" y="1298575"/>
           <a:chExt cx="3200400" cy="1828800"/>
         </a:xfrm>
@@ -29378,8 +29265,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2891155" y="1078230"/>
-          <a:ext cx="2774951" cy="815960"/>
+          <a:off x="2917825" y="1079500"/>
+          <a:ext cx="2813051" cy="817230"/>
           <a:chOff x="2917825" y="1079500"/>
           <a:chExt cx="2825751" cy="817230"/>
         </a:xfrm>
@@ -30417,8 +30304,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3695701" y="1045209"/>
-          <a:ext cx="3469621" cy="612143"/>
+          <a:off x="3733801" y="1047749"/>
+          <a:ext cx="3534391" cy="609603"/>
           <a:chOff x="3740151" y="1047749"/>
           <a:chExt cx="3529628" cy="609603"/>
         </a:xfrm>
@@ -31378,8 +31265,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="681355" y="1126490"/>
-          <a:ext cx="2832100" cy="695688"/>
+          <a:off x="688975" y="1123950"/>
+          <a:ext cx="2863850" cy="700768"/>
           <a:chOff x="688975" y="1123950"/>
           <a:chExt cx="2870200" cy="700768"/>
         </a:xfrm>
@@ -31522,8 +31409,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4512945" y="1126490"/>
-          <a:ext cx="2763203" cy="695688"/>
+          <a:off x="4556125" y="1123950"/>
+          <a:ext cx="2817813" cy="700768"/>
           <a:chOff x="4562475" y="1123950"/>
           <a:chExt cx="2819400" cy="700768"/>
         </a:xfrm>
@@ -31676,6 +31563,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -32169,7 +32060,11 @@
       </fieldGroup>
     </cacheField>
     <cacheField name="Buyer" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="Mom"/>
+        <s v="Dad"/>
+        <s v="Kelly"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Type" numFmtId="0">
       <sharedItems/>
@@ -32571,43 +32466,43 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="7">
   <r>
     <x v="0"/>
-    <s v="Mom"/>
+    <x v="0"/>
     <s v="Fuel"/>
     <n v="74"/>
   </r>
   <r>
     <x v="1"/>
-    <s v="Mom"/>
+    <x v="0"/>
     <s v="Food"/>
     <n v="235"/>
   </r>
   <r>
     <x v="2"/>
-    <s v="Dad"/>
+    <x v="1"/>
     <s v="Sports"/>
     <n v="20"/>
   </r>
   <r>
     <x v="3"/>
-    <s v="Kelly"/>
+    <x v="2"/>
     <s v="Books"/>
     <n v="125"/>
   </r>
   <r>
     <x v="4"/>
-    <s v="Mom"/>
+    <x v="0"/>
     <s v="Food"/>
     <n v="235"/>
   </r>
   <r>
     <x v="5"/>
-    <s v="Kelly"/>
+    <x v="2"/>
     <s v="Music"/>
     <n v="20"/>
   </r>
   <r>
     <x v="6"/>
-    <s v="Kelly"/>
+    <x v="2"/>
     <s v="Tickets"/>
     <n v="125"/>
   </r>
@@ -33133,8 +33028,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-1200-000000000000}" name="PivotTable Area" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="H14:J31" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-1200-000000000000}" name="PivotTable Area" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="H14:I18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0">
       <items count="369">
@@ -33509,9 +33404,16 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="44" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="44" outline="0" subtotalTop="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0">
       <items count="15">
         <item sd="0" x="0"/>
@@ -33532,6 +33434,29 @@
       </items>
     </pivotField>
   </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
   <formats count="2">
     <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
@@ -34097,7 +34022,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0B00-000000000000}" name="PivotTable11" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0B00-000000000000}" name="PivotTable11" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="H10:I14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField compact="0" numFmtId="16" outline="0" subtotalTop="0" showAll="0"/>
@@ -34847,34 +34772,34 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="11.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="115.77734375" style="17" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="17" customWidth="1"/>
-    <col min="3" max="16384" width="11.21875" style="17"/>
+    <col min="1" max="1" width="115.81640625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="3.54296875" style="17" customWidth="1"/>
+    <col min="3" max="16384" width="11.1796875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="59.4" x14ac:dyDescent="1.2">
-      <c r="A2" s="47" t="s">
+    <row r="2" spans="1:1" ht="59.5" x14ac:dyDescent="1.45">
+      <c r="A2" s="38" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="44.4" x14ac:dyDescent="0.45">
-      <c r="A3" s="48" t="s">
+    <row r="3" spans="1:1" ht="44" x14ac:dyDescent="0.5">
+      <c r="A3" s="39" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="200.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="200.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="18"/>
     </row>
   </sheetData>
@@ -34890,36 +34815,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B11" s="7" t="s">
         <v>3</v>
       </c>
@@ -34932,14 +34857,14 @@
       <c r="E11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="41" t="s">
         <v>4</v>
       </c>
       <c r="I11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B12" s="25">
         <v>42736</v>
       </c>
@@ -34952,14 +34877,14 @@
       <c r="E12" s="22">
         <v>74</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="41" t="s">
         <v>10</v>
       </c>
       <c r="I12" s="24">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13" s="26">
         <v>42750</v>
       </c>
@@ -34972,14 +34897,14 @@
       <c r="E13" s="23">
         <v>235</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="41" t="s">
         <v>13</v>
       </c>
       <c r="I13" s="24">
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="25">
         <v>42752</v>
       </c>
@@ -34992,14 +34917,14 @@
       <c r="E14" s="22">
         <v>20</v>
       </c>
-      <c r="H14" s="50" t="s">
+      <c r="H14" s="41" t="s">
         <v>8</v>
       </c>
       <c r="I14" s="24">
         <v>544</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="26">
         <v>42756</v>
       </c>
@@ -35019,7 +34944,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="25">
         <v>42768</v>
       </c>
@@ -35033,7 +34958,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="26">
         <v>42786</v>
       </c>
@@ -35047,7 +34972,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="25">
         <v>42791</v>
       </c>
@@ -35079,36 +35004,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -35121,14 +35046,14 @@
       <c r="E10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="50" t="s">
+      <c r="H10" s="41" t="s">
         <v>5</v>
       </c>
       <c r="I10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>42736</v>
       </c>
@@ -35141,14 +35066,14 @@
       <c r="E11" s="10">
         <v>74</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="41" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="24">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B12" s="6">
         <v>42750</v>
       </c>
@@ -35161,14 +35086,14 @@
       <c r="E12" s="11">
         <v>235</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="41" t="s">
         <v>11</v>
       </c>
       <c r="I12" s="24">
         <v>470</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>42752</v>
       </c>
@@ -35181,14 +35106,14 @@
       <c r="E13" s="10">
         <v>20</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="41" t="s">
         <v>9</v>
       </c>
       <c r="I13" s="24">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="6">
         <v>42756</v>
       </c>
@@ -35201,14 +35126,14 @@
       <c r="E14" s="11">
         <v>125</v>
       </c>
-      <c r="H14" s="50" t="s">
+      <c r="H14" s="41" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="24">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>42768</v>
       </c>
@@ -35221,14 +35146,14 @@
       <c r="E15" s="10">
         <v>235</v>
       </c>
-      <c r="H15" s="50" t="s">
+      <c r="H15" s="41" t="s">
         <v>12</v>
       </c>
       <c r="I15" s="24">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="6">
         <v>42786</v>
       </c>
@@ -35241,14 +35166,14 @@
       <c r="E16" s="11">
         <v>20</v>
       </c>
-      <c r="H16" s="50" t="s">
+      <c r="H16" s="41" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="24">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="5">
         <v>42791</v>
       </c>
@@ -35286,36 +35211,38 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -35328,14 +35255,14 @@
       <c r="E10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="50" t="s">
+      <c r="H10" s="42" t="s">
         <v>4</v>
       </c>
       <c r="I10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -35348,14 +35275,14 @@
       <c r="E11" s="22">
         <v>74</v>
       </c>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="42" t="s">
         <v>10</v>
       </c>
       <c r="I11" s="24">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -35368,14 +35295,14 @@
       <c r="E12" s="23">
         <v>235</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="42" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="24">
         <v>270</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -35388,14 +35315,14 @@
       <c r="E13" s="22">
         <v>20</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="42" t="s">
         <v>8</v>
       </c>
       <c r="I13" s="24">
         <v>544</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -35415,7 +35342,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -35429,7 +35356,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -35443,7 +35370,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -35475,41 +35402,41 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -35529,7 +35456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -35549,7 +35476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -35569,7 +35496,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -35589,7 +35516,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -35609,7 +35536,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -35623,7 +35550,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -35637,7 +35564,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -35669,43 +35596,43 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
-    <col min="5" max="6" width="10.21875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.81640625" style="2"/>
+    <col min="2" max="4" width="8.81640625" style="1"/>
+    <col min="5" max="6" width="10.1796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C14" s="7" t="s">
         <v>3</v>
       </c>
@@ -35719,7 +35646,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C15" s="25">
         <v>42736</v>
       </c>
@@ -35733,7 +35660,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C16" s="26">
         <v>42750</v>
       </c>
@@ -35747,7 +35674,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C17" s="25">
         <v>42752</v>
       </c>
@@ -35761,7 +35688,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C18" s="26">
         <v>42756</v>
       </c>
@@ -35775,7 +35702,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C19" s="25">
         <v>42768</v>
       </c>
@@ -35789,7 +35716,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C20" s="26">
         <v>42786</v>
       </c>
@@ -35803,7 +35730,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C21" s="25">
         <v>42791</v>
       </c>
@@ -35835,34 +35762,34 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.81640625" style="2"/>
+    <col min="2" max="4" width="8.81640625" style="1"/>
+    <col min="5" max="5" width="10.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="1"/>
+    <col min="7" max="7" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+    <row r="3" spans="1:1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="28" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -35882,46 +35809,46 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="13.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.81640625" style="2"/>
+    <col min="2" max="4" width="8.81640625" style="1"/>
+    <col min="5" max="5" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="1"/>
+    <col min="7" max="7" width="13.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12"/>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
@@ -35933,7 +35860,7 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="13"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -35943,7 +35870,7 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="13"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -35953,7 +35880,7 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="13"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -35963,7 +35890,7 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="13"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -35973,7 +35900,7 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" s="13"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -35983,7 +35910,7 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" s="13"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -35993,7 +35920,7 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" s="13"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -36003,70 +35930,70 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
@@ -36086,44 +36013,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="13.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.81640625" style="2"/>
+    <col min="2" max="4" width="8.81640625" style="1"/>
+    <col min="5" max="5" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="1"/>
+    <col min="7" max="7" width="13.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
@@ -36133,7 +36060,7 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="13"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -36141,7 +36068,7 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="13"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -36150,7 +36077,7 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="13"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -36159,7 +36086,7 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="13"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -36168,7 +36095,7 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" s="13"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -36177,7 +36104,7 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" s="13"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -36186,7 +36113,7 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" s="13"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -36195,52 +36122,52 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
@@ -36260,46 +36187,46 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="2" width="8.77734375" style="1"/>
-    <col min="3" max="3" width="8.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.81640625" style="2"/>
+    <col min="2" max="2" width="8.81640625" style="1"/>
+    <col min="3" max="3" width="8.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D12" s="8" t="s">
         <v>20</v>
       </c>
@@ -36307,7 +36234,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" s="12" t="s">
@@ -36319,7 +36246,7 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="13"/>
       <c r="C14"/>
       <c r="D14" s="12" t="s">
@@ -36331,7 +36258,7 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="13"/>
       <c r="C15"/>
       <c r="D15" s="12" t="s">
@@ -36344,7 +36271,7 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="13"/>
       <c r="C16"/>
       <c r="D16" s="12" t="s">
@@ -36357,7 +36284,7 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="13"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -36366,7 +36293,7 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" s="13"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -36375,7 +36302,7 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" s="13"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -36384,7 +36311,7 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" s="13"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -36393,52 +36320,52 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
@@ -36457,69 +36384,70 @@
   <sheetPr codeName="Sheet20">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="H10" s="20"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="H11" s="20"/>
     </row>
-    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
       <c r="H12" s="21" t="str">
         <f>IF(AND($H$14="Buyer",$I$18=834),"Good job! You placed the fields correctly."," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>Good job! You placed the fields correctly.</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="7" t="s">
         <v>3</v>
       </c>
@@ -36532,11 +36460,14 @@
       <c r="E14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="28"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="30"/>
+      <c r="H14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="25">
         <v>42736</v>
       </c>
@@ -36549,11 +36480,14 @@
       <c r="E15" s="22">
         <v>74</v>
       </c>
-      <c r="H15" s="31"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="33"/>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="24">
+        <v>20</v>
+      </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="26">
         <v>42750</v>
       </c>
@@ -36566,11 +36500,14 @@
       <c r="E16" s="23">
         <v>235</v>
       </c>
-      <c r="H16" s="31"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="33"/>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="24">
+        <v>270</v>
+      </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="25">
         <v>42752</v>
       </c>
@@ -36583,11 +36520,14 @@
       <c r="E17" s="22">
         <v>20</v>
       </c>
-      <c r="H17" s="31"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="33"/>
+      <c r="H17" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="24">
+        <v>544</v>
+      </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" s="26">
         <v>42756</v>
       </c>
@@ -36600,11 +36540,14 @@
       <c r="E18" s="23">
         <v>125</v>
       </c>
-      <c r="H18" s="31"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="33"/>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="24">
+        <v>834</v>
+      </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" s="25">
         <v>42768</v>
       </c>
@@ -36617,11 +36560,8 @@
       <c r="E19" s="22">
         <v>235</v>
       </c>
-      <c r="H19" s="31"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="33"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" s="26">
         <v>42786</v>
       </c>
@@ -36634,11 +36574,8 @@
       <c r="E20" s="23">
         <v>20</v>
       </c>
-      <c r="H20" s="31"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B21" s="25">
         <v>42791</v>
       </c>
@@ -36651,59 +36588,6 @@
       <c r="E21" s="22">
         <v>125</v>
       </c>
-      <c r="H21" s="31"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="33"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H22" s="31"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H23" s="31"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="33"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H24" s="31"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="33"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H25" s="31"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="33"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H26" s="31"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="33"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H27" s="31"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="33"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H28" s="31"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="33"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H29" s="31"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="33"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H30" s="31"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="33"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H31" s="34"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="36"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -36726,41 +36610,41 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="2" max="4" width="9.21875" style="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9.21875" style="1"/>
-    <col min="8" max="8" width="10.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.21875" style="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="2" max="4" width="9.1796875" style="1"/>
+    <col min="5" max="5" width="10.1796875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="9.1796875" style="1"/>
+    <col min="8" max="8" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="40"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -36780,7 +36664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -36800,7 +36684,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -36820,7 +36704,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -36840,7 +36724,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -36860,7 +36744,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -36874,7 +36758,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -36888,7 +36772,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -36918,49 +36802,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="4" width="8.77734375" style="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.81640625" style="2"/>
+    <col min="2" max="4" width="8.81640625" style="1"/>
+    <col min="5" max="5" width="10.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="1"/>
+    <col min="7" max="7" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -36976,159 +36860,159 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="41" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B15" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="33" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="43">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B16" s="34">
         <v>42736</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="36">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="44">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B17" s="35">
         <v>42750</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="37">
         <v>235</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="43">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B18" s="34">
         <v>42752</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="36">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="44">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B19" s="35">
         <v>42756</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="37">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="43">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B20" s="34">
         <v>42768</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="36">
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="44">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B21" s="35">
         <v>42786</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="46">
+      <c r="E21" s="37">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="43">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B22" s="34">
         <v>42791</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="36">
         <v>125</v>
       </c>
     </row>
@@ -37145,42 +37029,42 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.55" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="2"/>
-    <col min="2" max="2" width="95.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="2"/>
+    <col min="2" max="2" width="95.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="14" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B2"/>
     </row>
-    <row r="3" spans="1:2" s="14" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B3"/>
     </row>
-    <row r="4" spans="1:2" s="15" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" s="15" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A4" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B4"/>
     </row>
-    <row r="5" spans="1:2" s="16" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B5"/>
     </row>
-    <row r="6" spans="1:2" s="16" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>61</v>
       </c>
@@ -37207,37 +37091,37 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -37257,7 +37141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -37286,7 +37170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -37311,7 +37195,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -37336,7 +37220,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -37361,7 +37245,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -37386,7 +37270,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -37411,7 +37295,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -37436,7 +37320,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
       <c r="G18" t="s">
         <v>15</v>
       </c>
@@ -37471,39 +37355,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>3</v>
       </c>
@@ -37523,7 +37407,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -37552,7 +37436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -37577,7 +37461,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -37602,7 +37486,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -37627,7 +37511,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -37652,7 +37536,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -37677,7 +37561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -37702,7 +37586,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
       <c r="G18" s="12" t="s">
         <v>15</v>
       </c>
@@ -37737,35 +37621,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -37779,7 +37663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -37793,7 +37677,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -37807,7 +37691,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -37821,7 +37705,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -37835,7 +37719,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -37849,7 +37733,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -37863,7 +37747,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -37895,35 +37779,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -37937,7 +37821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -37951,7 +37835,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -37965,7 +37849,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -37979,7 +37863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -37993,7 +37877,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -38007,7 +37891,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -38021,7 +37905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -38053,33 +37937,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>3</v>
       </c>
@@ -38093,7 +37977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B11" s="25">
         <v>42736</v>
       </c>
@@ -38107,7 +37991,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B12" s="26">
         <v>42750</v>
       </c>
@@ -38121,7 +38005,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B13" s="25">
         <v>42752</v>
       </c>
@@ -38135,7 +38019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B14" s="26">
         <v>42756</v>
       </c>
@@ -38149,7 +38033,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B15" s="25">
         <v>42768</v>
       </c>
@@ -38163,7 +38047,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B16" s="26">
         <v>42786</v>
       </c>
@@ -38177,7 +38061,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="25">
         <v>42791</v>
       </c>
@@ -38209,39 +38093,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2" customWidth="1"/>
-    <col min="2" max="4" width="9.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="9.1796875" style="2" customWidth="1"/>
+    <col min="2" max="4" width="9.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="1"/>
+    <col min="7" max="7" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -38258,7 +38142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" s="5">
         <v>42736</v>
       </c>
@@ -38275,7 +38159,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="6">
         <v>42750</v>
       </c>
@@ -38289,7 +38173,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>42752</v>
       </c>
@@ -38303,7 +38187,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14" s="6">
         <v>42756</v>
       </c>
@@ -38317,7 +38201,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>42768</v>
       </c>
@@ -38331,7 +38215,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B16" s="6">
         <v>42786</v>
       </c>
@@ -38345,7 +38229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="5">
         <v>42791</v>
       </c>
@@ -38377,36 +38261,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="2"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" s="7" t="s">
         <v>3</v>
       </c>
@@ -38423,7 +38307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="25">
         <v>42736</v>
       </c>
@@ -38440,7 +38324,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13" s="26">
         <v>42750</v>
       </c>
@@ -38454,7 +38338,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14" s="25">
         <v>42752</v>
       </c>
@@ -38468,7 +38352,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15" s="26">
         <v>42756</v>
       </c>
@@ -38482,7 +38366,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B16" s="25">
         <v>42768</v>
       </c>
@@ -38496,7 +38380,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="26">
         <v>42786</v>
       </c>
@@ -38510,7 +38394,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="25">
         <v>42791</v>
       </c>
